--- a/workshop/aadd8b9bfa.xlsx
+++ b/workshop/aadd8b9bfa.xlsx
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>0.7-1.6 秒/镜，3-4 镜快切</t>
+          <t>0.9-1.9 秒/镜，2-3 镜快切</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>这 3 秒决定完播，画面要「炸」，配重音效</t>
+          <t>这 3 秒决定完播，画面要「炸」，配重音效。⚠️别再切碎到 0.8 秒——TTS/真人都会读得发赶，听着假</t>
         </is>
       </c>
     </row>

--- a/workshop/aadd8b9bfa.xlsx
+++ b/workshop/aadd8b9bfa.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -2233,161 +2233,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>检索词（英文，主用）</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>建议条数</t>
-        </is>
-      </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>账本单据</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>005、009、013、017、021、025、029</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>cash register / counting money / ledger red ink</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>办公室</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>006、010、014、018、022、026、030</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>worried businessman / empty office</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>数据图表</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>003、007、011、015、019、023、027</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>cash flow chart / downward arrow</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>厂房外景</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>004、008、012、016、020、024、028</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>factory exterior / for lease sign</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>005、009、014、024-025、030</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>片尾落点 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>031-032</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自己拍</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>办公室</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>worried businessman / empty office</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>数据图表</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>cash flow chart / downward arrow</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>厂房外景</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>factory exterior / for lease sign</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>L3 AI 兜底</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>仅在实拍和素材站都拿不到时启用</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/aadd8b9bfa.xlsx
+++ b/workshop/aadd8b9bfa.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2233,417 +2233,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>序号</t>
+          <t>场景</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>层级</t>
+          <t>检索词（英文，主用）</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
-          <t>场景</t>
+          <t>建议条数</t>
         </is>
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>覆盖镜次</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>怎么做（检索词 / 拍摄内容）</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>去哪找</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>要几条</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="5" t="inlineStr"/>
-      <c r="B2" s="5" t="inlineStr">
+          <t>来源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>L1 自拍</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>片头钩子 · 自拍空镜</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>001-002</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr">
-        <is>
-          <t>自己拍（手机横屏）</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="7" t="inlineStr"/>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>账本单据</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>cash register / counting money / ledger red ink</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>办公室</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>worried businessman / empty office</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>账本单据</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>005、009、013、017、021、025、029</t>
-        </is>
-      </c>
-      <c r="F3" s="8" t="inlineStr">
-        <is>
-          <t>cash register / counting money / ledger red ink</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I3" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="inlineStr"/>
-      <c r="B4" s="7" t="inlineStr">
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>数据图表</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>cash flow chart / downward arrow</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>办公室</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>006、010、014、018、022、026、030</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>worried businessman / empty office</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>厂房外景</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>factory exterior / for lease sign</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>数据图表</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>003、007、011、015、019、023、027</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>cash flow chart / downward arrow</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr"/>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>L2 免费站</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>厂房外景</t>
-        </is>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>004、008、012、016、020、024、028</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>factory exterior / for lease sign</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名、可商用）</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>本片复用 7 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>L1 自制</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>数据图表 · Excel 出图（叠加层）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>005、009、014、024-025、030</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="5" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>L1 自拍</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>片尾落点 · 自拍空镜</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>031-032</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>自己拍</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>L3 AI 兜底</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>仅在实拍和素材站都拿不到时启用</t>
-        </is>
-      </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>按需</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名可商用）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
